--- a/Gantt-projekttervező1.xlsx
+++ b/Gantt-projekttervező1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20380"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E62C5D5B-B970-40F9-BB37-C6958C788F9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57231FB8-8DCD-4716-8BBD-0E7B6EA8D1E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="28830" windowHeight="16110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2132,7 +2132,7 @@
         <v>19</v>
       </c>
       <c r="G11" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
